--- a/tests/gold-project/outputs/schedule/Shooting schedule.xlsx
+++ b/tests/gold-project/outputs/schedule/Shooting schedule.xlsx
@@ -143,7 +143,7 @@
     <t>19:00</t>
   </si>
   <si>
-    <t>Flashback. In the dark Mariamma connects the battery set. Joe leaves. Young Anjali watche…</t>
+    <t>Flashback. In the dark Mariamma connects the battery set. Joe leaves. Young Anjali watches.</t>
   </si>
   <si>
     <t>JOE (Lal Fernandez), MARIAMMA (Divya Mathew), YOUNG ANJALI (Ameya Suresh)</t>
@@ -158,7 +158,7 @@
     <t>INT. COAST RADIO STATION - OPERATIONS ROOM - NIGHT</t>
   </si>
   <si>
-    <t>Anjali and Rahul let themselves in. The tape shelves are empty except for one reel dated …</t>
+    <t>Anjali and Rahul let themselves in. The tape shelves are empty except for one reel dated 14-11-1999.</t>
   </si>
   <si>
     <t>RAHUL (Aditya Nair), ANJALI (Nimisha Raghavan)</t>
@@ -221,7 +221,7 @@
     <t>EXT. COAST RADIO STATION - DAWN</t>
   </si>
   <si>
-    <t>Anjali arrives. Appachan sits at the foot of the mast with his dog Kannan. Inspector Lath…</t>
+    <t>Anjali arrives. Appachan sits at the foot of the mast with his dog Kannan. Inspector Latha waits by her jeep.</t>
   </si>
   <si>
     <t>LATHA (Reshmi Pillai), APPACHAN (K. P. Gopinathan), ANJALI (Nimisha Raghavan)</t>
@@ -329,7 +329,7 @@
     <t>Tea Shop and Toddy Shop Row (Mattancherry)</t>
   </si>
   <si>
-    <t>The school radio club meets over tea. Rahul asks Anjali to look at their homemade transmi…</t>
+    <t>The school radio club meets over tea. Rahul asks Anjali to look at their homemade transmitter.</t>
   </si>
   <si>
     <t>MEENU (Gauri Krishna), RAHUL (Aditya Nair), FATHIMA (Sabitha Rasheed), Nurse, ANJALI (Nimisha Raghavan)</t>
@@ -398,7 +398,7 @@
     <t>Government Fisheries School Laboratory (Kalamassery)</t>
   </si>
   <si>
-    <t>Anjali examines the reel. Sticky-shed damage. It has to be baked before it can be played …</t>
+    <t>Anjali examines the reel. Sticky-shed damage. It has to be baked before it can be played once.</t>
   </si>
   <si>
     <t>MEENU (Gauri Krishna), RAHUL (Aditya Nair), FATHIMA (Sabitha Rasheed), ANJALI (Nimisha Raghavan)</t>
@@ -467,7 +467,7 @@
     <t>EXT. KADALKKARA HARBOUR - DAY</t>
   </si>
   <si>
-    <t>Anjali walks the harbour. Fishermen remember her mother. Suresh runs a survey crew and do…</t>
+    <t>Anjali walks the harbour. Fishermen remember her mother. Suresh runs a survey crew and does not want her there.</t>
   </si>
   <si>
     <t>Old Fisherman, SURESH (Sajan Kuriakose), ANJALI (Nimisha Raghavan)</t>
@@ -554,7 +554,7 @@
     <t>Munambam Breakwater (stunt section)</t>
   </si>
   <si>
-    <t>Suresh finds Appachan at the end of the breakwater with Kannan, waving a torch at the sea…</t>
+    <t>Suresh finds Appachan at the end of the breakwater with Kannan, waving a torch at the sea. He carries him back.</t>
   </si>
   <si>
     <t>SURESH (Sajan Kuriakose), APPACHAN (K. P. Gopinathan), ANJALI (Nimisha Raghavan)</t>
@@ -620,7 +620,7 @@
     <t>St. Antony's Church (Kadalkkara set dressing)</t>
   </si>
   <si>
-    <t>The memorial mass for the men lost in 1999. Suresh reads the names. Anjali stands at the …</t>
+    <t>The memorial mass for the men lost in 1999. Suresh reads the names. Anjali stands at the back.</t>
   </si>
   <si>
     <t>SURESH (Sajan Kuriakose), FATHIMA (Sabitha Rasheed), ANJALI (Nimisha Raghavan)</t>
@@ -788,7 +788,7 @@
     <t>Soundwave Studio (Kochi stand-in for Bengaluru)</t>
   </si>
   <si>
-    <t>Present day. Anjali scrubs breaths out of a detergent ad. Fathima calls: Appachan is miss…</t>
+    <t>Present day. Anjali scrubs breaths out of a detergent ad. Fathima calls: Appachan is missing.</t>
   </si>
   <si>
     <t>STUDIO PRODUCER (Karan Shetty), FATHIMA (Sabitha Rasheed), ANJALI (Nimisha Raghavan)</t>
@@ -836,7 +836,7 @@
     <t>Open Sea off Vypin (2 nautical miles out)</t>
   </si>
   <si>
-    <t>Prologue. A storm. Fishing boats in the swell and a woman's voice on the radio reading po…</t>
+    <t>Prologue. A storm. Fishing boats in the swell and a woman's voice on the radio reading positions.</t>
   </si>
   <si>
     <t>MARIAMMA (Divya Mathew), VARGHESE (Thampi Cherian)</t>
@@ -845,7 +845,7 @@
     <t>EXT. OPEN SEA - LITTLE FLOWER - NIGHT (1999)</t>
   </si>
   <si>
-    <t>Flashback. Varghese turns the fleet toward the river mouth, then goes back for the Seagul…</t>
+    <t>Flashback. Varghese turns the fleet toward the river mouth, then goes back for the Seagull.</t>
   </si>
   <si>
     <t>VARGHESE (Thampi Cherian), MARIAMMA (Divya Mathew)</t>
@@ -4062,7 +4062,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
   <headerFooter>
-    <oddFooter>&amp;CCreated with OpenFrame Studio</oddFooter>
+    <oddFooter>&amp;CCreated using OpenFrame</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
